--- a/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
+++ b/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8581" uniqueCount="4126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8608" uniqueCount="4143">
   <si>
     <t>sheet</t>
   </si>
@@ -12017,7 +12017,7 @@
     <t>01_Processing/01_Protein_Filtering/c_data/protein_filtering.xlsx</t>
   </si>
   <si>
-    <t>2d3d08a0b41566454648891cedbdc9e5</t>
+    <t>3102d0df52e0fab024dc7ec2c3c621f0</t>
   </si>
   <si>
     <t>normalize</t>
@@ -12026,7 +12026,7 @@
     <t>01_Processing/02_Normalisation/c_data/normalisation.xlsx</t>
   </si>
   <si>
-    <t>e95241c7fd06ca6de75a3a01171c882b</t>
+    <t>2f44be801ba0e49d9bb46b37d4e57cc8</t>
   </si>
   <si>
     <t>quantify</t>
@@ -12035,7 +12035,7 @@
     <t>01_Processing/03_Quantification/c_data/quantification.xlsx</t>
   </si>
   <si>
-    <t>1ea361e7f4f41a8e1a7852847f4032b0</t>
+    <t>066cca64dce1a459267075843405a238</t>
   </si>
   <si>
     <t>contrasts</t>
@@ -12044,7 +12044,7 @@
     <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>0d6cf853ff8d0d35c8767a6734aeecb9</t>
+    <t>4a09b3edb7bc9a8d0cee075927563827</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -12149,12 +12149,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -12212,6 +12224,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -12224,6 +12248,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -12233,9 +12269,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -12248,6 +12281,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -12329,6 +12368,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -12399,6 +12444,12 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -13153,7 +13204,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -13414,7 +13465,7 @@
         <v>4052</v>
       </c>
       <c r="B24" t="s">
-        <v>4045</v>
+        <v>4053</v>
       </c>
       <c r="C24" t="s">
         <v>4011</v>
@@ -13422,10 +13473,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="B25" t="s">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="C25" t="s">
         <v>4011</v>
@@ -13433,10 +13484,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="B26" t="s">
-        <v>4056</v>
+        <v>4049</v>
       </c>
       <c r="C26" t="s">
         <v>4011</v>
@@ -13472,7 +13523,7 @@
         <v>4062</v>
       </c>
       <c r="C29" t="s">
-        <v>4008</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -13516,7 +13567,7 @@
         <v>4070</v>
       </c>
       <c r="C33" t="s">
-        <v>4011</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -13568,7 +13619,7 @@
         <v>4079</v>
       </c>
       <c r="B38" t="s">
-        <v>4080</v>
+        <v>4041</v>
       </c>
       <c r="C38" t="s">
         <v>4011</v>
@@ -13576,10 +13627,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>4080</v>
+      </c>
+      <c r="B39" t="s">
         <v>4081</v>
-      </c>
-      <c r="B39" t="s">
-        <v>4082</v>
       </c>
       <c r="C39" t="s">
         <v>4011</v>
@@ -13587,10 +13638,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>4082</v>
+      </c>
+      <c r="B40" t="s">
         <v>4083</v>
-      </c>
-      <c r="B40" t="s">
-        <v>4084</v>
       </c>
       <c r="C40" t="s">
         <v>4011</v>
@@ -13598,10 +13649,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>4084</v>
+      </c>
+      <c r="B41" t="s">
         <v>4085</v>
-      </c>
-      <c r="B41" t="s">
-        <v>4086</v>
       </c>
       <c r="C41" t="s">
         <v>4011</v>
@@ -13609,10 +13660,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>4086</v>
+      </c>
+      <c r="B42" t="s">
         <v>4087</v>
-      </c>
-      <c r="B42" t="s">
-        <v>4088</v>
       </c>
       <c r="C42" t="s">
         <v>4011</v>
@@ -13620,10 +13671,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>4088</v>
+      </c>
+      <c r="B43" t="s">
         <v>4089</v>
-      </c>
-      <c r="B43" t="s">
-        <v>4090</v>
       </c>
       <c r="C43" t="s">
         <v>4011</v>
@@ -13631,10 +13682,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>4090</v>
+      </c>
+      <c r="B44" t="s">
         <v>4091</v>
-      </c>
-      <c r="B44" t="s">
-        <v>4092</v>
       </c>
       <c r="C44" t="s">
         <v>4011</v>
@@ -13642,10 +13693,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>4092</v>
+      </c>
+      <c r="B45" t="s">
         <v>4093</v>
-      </c>
-      <c r="B45" t="s">
-        <v>4094</v>
       </c>
       <c r="C45" t="s">
         <v>4011</v>
@@ -13653,10 +13704,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>4094</v>
+      </c>
+      <c r="B46" t="s">
         <v>4095</v>
-      </c>
-      <c r="B46" t="s">
-        <v>4096</v>
       </c>
       <c r="C46" t="s">
         <v>4011</v>
@@ -13664,21 +13715,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
+        <v>4096</v>
+      </c>
+      <c r="B47" t="s">
         <v>4097</v>
       </c>
-      <c r="B47" t="s">
-        <v>4098</v>
-      </c>
       <c r="C47" t="s">
-        <v>4099</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>4100</v>
+        <v>4098</v>
       </c>
       <c r="B48" t="s">
-        <v>4101</v>
+        <v>4099</v>
       </c>
       <c r="C48" t="s">
         <v>4011</v>
@@ -13686,21 +13737,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>4102</v>
+        <v>4100</v>
       </c>
       <c r="B49" t="s">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="C49" t="s">
-        <v>4008</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="B50" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="C50" t="s">
         <v>4011</v>
@@ -13708,10 +13759,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>4106</v>
+        <v>4104</v>
       </c>
       <c r="B51" t="s">
-        <v>4107</v>
+        <v>4105</v>
       </c>
       <c r="C51" t="s">
         <v>4011</v>
@@ -13719,10 +13770,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>4108</v>
+        <v>4106</v>
       </c>
       <c r="B52" t="s">
-        <v>4109</v>
+        <v>4107</v>
       </c>
       <c r="C52" t="s">
         <v>4011</v>
@@ -13730,10 +13781,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="B53" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="C53" t="s">
         <v>4011</v>
@@ -13741,21 +13792,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>4110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4111</v>
+      </c>
+      <c r="C54" t="s">
         <v>4112</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4113</v>
-      </c>
-      <c r="C54" t="s">
-        <v>4011</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
+        <v>4113</v>
+      </c>
+      <c r="B55" t="s">
         <v>4114</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4074</v>
       </c>
       <c r="C55" t="s">
         <v>4011</v>
@@ -13766,7 +13817,7 @@
         <v>4115</v>
       </c>
       <c r="B56" t="s">
-        <v>4039</v>
+        <v>4116</v>
       </c>
       <c r="C56" t="s">
         <v>4011</v>
@@ -13774,21 +13825,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>4116</v>
+        <v>4117</v>
       </c>
       <c r="B57" t="s">
-        <v>4117</v>
+        <v>4118</v>
       </c>
       <c r="C57" t="s">
-        <v>4011</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>4118</v>
+        <v>4119</v>
       </c>
       <c r="B58" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="C58" t="s">
         <v>4011</v>
@@ -13796,10 +13847,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="B59" t="s">
-        <v>4121</v>
+        <v>4122</v>
       </c>
       <c r="C59" t="s">
         <v>4011</v>
@@ -13807,10 +13858,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="B60" t="s">
-        <v>4123</v>
+        <v>4124</v>
       </c>
       <c r="C60" t="s">
         <v>4011</v>
@@ -13818,12 +13869,111 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="B61" t="s">
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="C61" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>4127</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4128</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>4129</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4087</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>4130</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4039</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>4131</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4132</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>4133</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4134</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>4135</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4136</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>4137</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4138</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>4139</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>4141</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4142</v>
+      </c>
+      <c r="C70" t="s">
         <v>4011</v>
       </c>
     </row>

--- a/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
+++ b/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
@@ -12017,7 +12017,7 @@
     <t>01_Processing/01_Protein_Filtering/c_data/protein_filtering.xlsx</t>
   </si>
   <si>
-    <t>3102d0df52e0fab024dc7ec2c3c621f0</t>
+    <t>4d0571477e252bda504280fcf8810abb</t>
   </si>
   <si>
     <t>normalize</t>
@@ -12026,7 +12026,7 @@
     <t>01_Processing/02_Normalisation/c_data/normalisation.xlsx</t>
   </si>
   <si>
-    <t>2f44be801ba0e49d9bb46b37d4e57cc8</t>
+    <t>da24faf4c561a32ca2415aebed3f1d43</t>
   </si>
   <si>
     <t>quantify</t>
@@ -12035,7 +12035,7 @@
     <t>01_Processing/03_Quantification/c_data/quantification.xlsx</t>
   </si>
   <si>
-    <t>066cca64dce1a459267075843405a238</t>
+    <t>d915b5214529c0740dd29b7e2e009be0</t>
   </si>
   <si>
     <t>contrasts</t>
@@ -12044,7 +12044,7 @@
     <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>4a09b3edb7bc9a8d0cee075927563827</t>
+    <t>6bb93683143c481fb5481529db64870c</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
+++ b/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8608" uniqueCount="4143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8581" uniqueCount="4126">
   <si>
     <t>sheet</t>
   </si>
@@ -12041,10 +12041,10 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Group_comparisons/HRvLR/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>6bb93683143c481fb5481529db64870c</t>
+    <t>03_Group_comparisons/HRvLR/c_data/02_protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>c128a1560d3239cecce9981259007118</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -12149,126 +12149,93 @@
     <t>1.2.1</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggrepel</t>
+  </si>
+  <si>
+    <t>0.9.8</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggrepel</t>
-  </si>
-  <si>
-    <t>0.9.8</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -12281,12 +12248,6 @@
     <t>1.5.0</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -12368,12 +12329,6 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
-  </si>
-  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -12444,12 +12399,6 @@
   </si>
   <si>
     <t>3.0.2</t>
-  </si>
-  <si>
-    <t>xfun</t>
-  </si>
-  <si>
-    <t>0.57</t>
   </si>
   <si>
     <t>yaml</t>
@@ -13204,7 +13153,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -13465,7 +13414,7 @@
         <v>4052</v>
       </c>
       <c r="B24" t="s">
-        <v>4053</v>
+        <v>4045</v>
       </c>
       <c r="C24" t="s">
         <v>4011</v>
@@ -13473,10 +13422,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>4053</v>
+      </c>
+      <c r="B25" t="s">
         <v>4054</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4055</v>
       </c>
       <c r="C25" t="s">
         <v>4011</v>
@@ -13484,10 +13433,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>4055</v>
+      </c>
+      <c r="B26" t="s">
         <v>4056</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4049</v>
       </c>
       <c r="C26" t="s">
         <v>4011</v>
@@ -13523,7 +13472,7 @@
         <v>4062</v>
       </c>
       <c r="C29" t="s">
-        <v>4011</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -13567,7 +13516,7 @@
         <v>4070</v>
       </c>
       <c r="C33" t="s">
-        <v>4008</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -13619,7 +13568,7 @@
         <v>4079</v>
       </c>
       <c r="B38" t="s">
-        <v>4041</v>
+        <v>4080</v>
       </c>
       <c r="C38" t="s">
         <v>4011</v>
@@ -13627,10 +13576,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="B39" t="s">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C39" t="s">
         <v>4011</v>
@@ -13638,10 +13587,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>4082</v>
+        <v>4083</v>
       </c>
       <c r="B40" t="s">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="C40" t="s">
         <v>4011</v>
@@ -13649,10 +13598,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="B41" t="s">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="C41" t="s">
         <v>4011</v>
@@ -13660,10 +13609,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>4086</v>
+        <v>4087</v>
       </c>
       <c r="B42" t="s">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C42" t="s">
         <v>4011</v>
@@ -13671,10 +13620,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="B43" t="s">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="C43" t="s">
         <v>4011</v>
@@ -13682,10 +13631,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="B44" t="s">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="C44" t="s">
         <v>4011</v>
@@ -13693,10 +13642,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="B45" t="s">
-        <v>4093</v>
+        <v>4094</v>
       </c>
       <c r="C45" t="s">
         <v>4011</v>
@@ -13704,10 +13653,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="B46" t="s">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="C46" t="s">
         <v>4011</v>
@@ -13715,21 +13664,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="B47" t="s">
-        <v>4097</v>
+        <v>4098</v>
       </c>
       <c r="C47" t="s">
-        <v>4011</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>4098</v>
+        <v>4100</v>
       </c>
       <c r="B48" t="s">
-        <v>4099</v>
+        <v>4101</v>
       </c>
       <c r="C48" t="s">
         <v>4011</v>
@@ -13737,21 +13686,21 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>4100</v>
+        <v>4102</v>
       </c>
       <c r="B49" t="s">
-        <v>4101</v>
+        <v>4103</v>
       </c>
       <c r="C49" t="s">
-        <v>4011</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>4102</v>
+        <v>4104</v>
       </c>
       <c r="B50" t="s">
-        <v>4103</v>
+        <v>4105</v>
       </c>
       <c r="C50" t="s">
         <v>4011</v>
@@ -13759,10 +13708,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>4104</v>
+        <v>4106</v>
       </c>
       <c r="B51" t="s">
-        <v>4105</v>
+        <v>4107</v>
       </c>
       <c r="C51" t="s">
         <v>4011</v>
@@ -13770,10 +13719,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>4106</v>
+        <v>4108</v>
       </c>
       <c r="B52" t="s">
-        <v>4107</v>
+        <v>4109</v>
       </c>
       <c r="C52" t="s">
         <v>4011</v>
@@ -13781,10 +13730,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>4108</v>
+        <v>4110</v>
       </c>
       <c r="B53" t="s">
-        <v>4109</v>
+        <v>4111</v>
       </c>
       <c r="C53" t="s">
         <v>4011</v>
@@ -13792,21 +13741,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>4110</v>
+        <v>4112</v>
       </c>
       <c r="B54" t="s">
-        <v>4111</v>
+        <v>4113</v>
       </c>
       <c r="C54" t="s">
-        <v>4112</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>4113</v>
+        <v>4114</v>
       </c>
       <c r="B55" t="s">
-        <v>4114</v>
+        <v>4074</v>
       </c>
       <c r="C55" t="s">
         <v>4011</v>
@@ -13817,7 +13766,7 @@
         <v>4115</v>
       </c>
       <c r="B56" t="s">
-        <v>4116</v>
+        <v>4039</v>
       </c>
       <c r="C56" t="s">
         <v>4011</v>
@@ -13825,21 +13774,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
+        <v>4116</v>
+      </c>
+      <c r="B57" t="s">
         <v>4117</v>
       </c>
-      <c r="B57" t="s">
-        <v>4118</v>
-      </c>
       <c r="C57" t="s">
-        <v>4008</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>4118</v>
+      </c>
+      <c r="B58" t="s">
         <v>4119</v>
-      </c>
-      <c r="B58" t="s">
-        <v>4120</v>
       </c>
       <c r="C58" t="s">
         <v>4011</v>
@@ -13847,10 +13796,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>4120</v>
+      </c>
+      <c r="B59" t="s">
         <v>4121</v>
-      </c>
-      <c r="B59" t="s">
-        <v>4122</v>
       </c>
       <c r="C59" t="s">
         <v>4011</v>
@@ -13858,10 +13807,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>4122</v>
+      </c>
+      <c r="B60" t="s">
         <v>4123</v>
-      </c>
-      <c r="B60" t="s">
-        <v>4124</v>
       </c>
       <c r="C60" t="s">
         <v>4011</v>
@@ -13869,111 +13818,12 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>4124</v>
+      </c>
+      <c r="B61" t="s">
         <v>4125</v>
       </c>
-      <c r="B61" t="s">
-        <v>4126</v>
-      </c>
       <c r="C61" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>4127</v>
-      </c>
-      <c r="B62" t="s">
-        <v>4128</v>
-      </c>
-      <c r="C62" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>4129</v>
-      </c>
-      <c r="B63" t="s">
-        <v>4087</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" t="s">
-        <v>4130</v>
-      </c>
-      <c r="B64" t="s">
-        <v>4039</v>
-      </c>
-      <c r="C64" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" t="s">
-        <v>4131</v>
-      </c>
-      <c r="B65" t="s">
-        <v>4132</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" t="s">
-        <v>4133</v>
-      </c>
-      <c r="B66" t="s">
-        <v>4134</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" t="s">
-        <v>4135</v>
-      </c>
-      <c r="B67" t="s">
-        <v>4136</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" t="s">
-        <v>4137</v>
-      </c>
-      <c r="B68" t="s">
-        <v>4138</v>
-      </c>
-      <c r="C68" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" t="s">
-        <v>4139</v>
-      </c>
-      <c r="B69" t="s">
-        <v>4140</v>
-      </c>
-      <c r="C69" t="s">
-        <v>4011</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" t="s">
-        <v>4141</v>
-      </c>
-      <c r="B70" t="s">
-        <v>4142</v>
-      </c>
-      <c r="C70" t="s">
         <v>4011</v>
       </c>
     </row>

--- a/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
+++ b/05_Figures/Processing/S01_QC/c_data/s01_qc.xlsx
@@ -149,10 +149,10 @@
     <t>Participant identifier.</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>timepoint</t>
@@ -12017,7 +12017,7 @@
     <t>01_Processing/01_Protein_Filtering/c_data/protein_filtering.xlsx</t>
   </si>
   <si>
-    <t>4d0571477e252bda504280fcf8810abb</t>
+    <t>183224f1e1393e2d414c947e26a03219</t>
   </si>
   <si>
     <t>normalize</t>
@@ -12026,7 +12026,7 @@
     <t>01_Processing/02_Normalisation/c_data/normalisation.xlsx</t>
   </si>
   <si>
-    <t>da24faf4c561a32ca2415aebed3f1d43</t>
+    <t>1f9ebc002b278f8b6e2536f38d876613</t>
   </si>
   <si>
     <t>quantify</t>
@@ -12035,7 +12035,7 @@
     <t>01_Processing/03_Quantification/c_data/quantification.xlsx</t>
   </si>
   <si>
-    <t>d915b5214529c0740dd29b7e2e009be0</t>
+    <t>45d5f62faae23008c5e43fd9a236c172</t>
   </si>
   <si>
     <t>contrasts</t>
@@ -12044,7 +12044,7 @@
     <t>03_Group_comparisons/HRvLR/c_data/02_protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>c128a1560d3239cecce9981259007118</t>
+    <t>6513b98af7f564bb10c517dbdd3ee251</t>
   </si>
   <si>
     <t>BiocGenerics</t>
